--- a/artfynd/A 23846-2026 artfynd.xlsx
+++ b/artfynd/A 23846-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80672133</v>
+        <v>133920290</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stora Envättern, Ö om, Srm</t>
+          <t>V Römossjön, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634742.2322889095</v>
+        <v>634757</v>
       </c>
       <c r="R2" t="n">
-        <v>6554670.904207534</v>
+        <v>6554123</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-10-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-10-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,34 +773,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Gustaf Eibl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Gustaf Eibl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80672309</v>
+        <v>80672131</v>
       </c>
       <c r="B3" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634678.9279196083</v>
+        <v>634780</v>
       </c>
       <c r="R3" t="n">
-        <v>6554640.917500641</v>
+        <v>6554693</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,19 +863,9 @@
           <t>2019-10-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-10-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -914,15 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80672192</v>
+        <v>80672132</v>
       </c>
       <c r="B4" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634689.1663297112</v>
+        <v>634777</v>
       </c>
       <c r="R4" t="n">
-        <v>6554657.211769857</v>
+        <v>6554680</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,19 +970,14 @@
           <t>2019-10-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-10-30</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På en fälld gammal eklåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,63 +1005,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>85336525</v>
+        <v>80672309</v>
       </c>
       <c r="B5" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Römossjön, Södertälje kommun, Svealand, Sjundavägen, Sjundatorp, Stockholms, Srm</t>
+          <t>Stora Envättern, Ö om, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>634748.5166295306</v>
+        <v>634679</v>
       </c>
       <c r="R5" t="n">
-        <v>6554142.206246274</v>
+        <v>6554641</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1111,22 +1074,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-05-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2019-10-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-05-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2019-10-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gammal tallstubbe.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,33 +1093,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gustaf Eibl</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gustaf Eibl</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>86633945</v>
+        <v>80672133</v>
       </c>
       <c r="B6" t="n">
-        <v>44577</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,66 +1123,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208307</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pudrad kärrtrollslända</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucorrhinia albifrons</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Burmeister, 1839)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skogsvägen Römossjön, Srm</t>
+          <t>Stora Envättern, Ö om, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>634922.3362667226</v>
+        <v>634742</v>
       </c>
       <c r="R6" t="n">
-        <v>6554571.892471388</v>
+        <v>6554671</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1252,22 +1181,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2019-10-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2019-10-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,27 +1202,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Holmberg</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Holmberg</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>86633955</v>
+        <v>80672192</v>
       </c>
       <c r="B7" t="n">
-        <v>44578</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,66 +1225,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208306</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bred kärrtrollslända</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucorrhinia caudalis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Charpentier, 1840)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skogsvägen Römossjön, Srm</t>
+          <t>Stora Envättern, Ö om, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>634922.3362667226</v>
+        <v>634689</v>
       </c>
       <c r="R7" t="n">
-        <v>6554571.892471388</v>
+        <v>6554657</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1394,22 +1283,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2019-10-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2019-10-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,27 +1304,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Holmberg</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Holmberg</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102317916</v>
+        <v>133920300</v>
       </c>
       <c r="B8" t="n">
-        <v>44580</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,58 +1327,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102918</v>
+        <v>2558</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Citronfläckad kärrtrollslända</t>
+          <t>Krushättemossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucorrhinia pectoralis</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Charpentier, 1825)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>Ulota crispa s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skogsvägen Römossjön, Srm</t>
+          <t>V Römossjön, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>634922.3362667226</v>
+        <v>634673</v>
       </c>
       <c r="R8" t="n">
-        <v>6554571.892471388</v>
+        <v>6554140</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1528,22 +1382,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1552,22 +1406,2405 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Holmberg</t>
+          <t>Gustaf Eibl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Holmberg</t>
+          <t>Gustaf Eibl</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133920310</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96106</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2558</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Krushättemossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ulota crispa s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>V Römossjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>634603</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6554239</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>80828360</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93222</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellodon fuligineoalbus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stora Envättern, S om, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>634656</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6554805</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-11-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-11-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gammal tallskog.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>85336564</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92348</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Römossjön, Södertälje kommun, Svealand, Sjundavägen, Sjundatorp, Stockholms, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>634794</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6554162</v>
+      </c>
+      <c r="S11" t="n">
+        <v>17</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>80672538</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stora Envättern, Ö om, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>634658</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6554769</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2019-10-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2019-10-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>80780664</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stora Envättern, S om, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>634633</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6554574</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2019-11-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2019-11-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>80780677</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stora Envättern, S om, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>634628</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6554604</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2019-11-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2019-11-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>85336525</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Römossjön, Södertälje kommun, Svealand, Sjundavägen, Sjundatorp, Stockholms, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>634749</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6554142</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>80672093</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stora Envättern, Ö om, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>634734</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6554722</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2019-10-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2019-10-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>80672518</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stora Envättern, Ö om, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>634643</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6554697</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2019-10-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2019-10-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>80672529</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stora Envättern, Ö om, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>634663</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6554700</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2019-10-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2019-10-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>80780864</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stora Envättern, S om, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>634656</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6554805</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2019-11-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2019-11-06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133920302</v>
+      </c>
+      <c r="B20" t="n">
+        <v>81031</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6444</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skriftlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Graphis scripta</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>V Römossjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>634670</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6554141</v>
+      </c>
+      <c r="S20" t="n">
+        <v>14</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133920308</v>
+      </c>
+      <c r="B21" t="n">
+        <v>81031</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6444</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skriftlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Graphis scripta</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>V Römossjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>634603</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6554239</v>
+      </c>
+      <c r="S21" t="n">
+        <v>12</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>85356721</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57258</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Römossjön, Södertälje kommun, Svealand, Sjundavägen, Sjundatorp, Stockholms, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>634835</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6554254</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>80672511</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stora Envättern, Ö om, Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>634620</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6554556</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2019-10-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2019-10-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Tjäderspillning under gammal tall med typisk tjäderbetad form i anslutning till bergbunden mark.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>80780562</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stora Envättern, S om, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>634623</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6554561</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2019-11-06</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2019-11-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spillning under typisk tjäderbetad gammal tall. l</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133920298</v>
+      </c>
+      <c r="B25" t="n">
+        <v>44182</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>V Römossjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>634660</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6554108</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>80779827</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stora Envättern, S om, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>634583</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6554572</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2019-11-06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2019-11-06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Enstaka kläckhål i barken på gammal gran.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>102317916</v>
+      </c>
+      <c r="B27" t="n">
+        <v>45300</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>102918</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Citronfläckad kärrtrollslända</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Leucorrhinia pectoralis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Charpentier, 1825)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skogsvägen Römossjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>634922</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6554572</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Göran E Holmberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Göran E Holmberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>86633955</v>
+      </c>
+      <c r="B28" t="n">
+        <v>45298</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>208306</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bred kärrtrollslända</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Leucorrhinia caudalis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Charpentier, 1840)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skogsvägen Römossjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>634922</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6554572</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Göran E Holmberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Göran E Holmberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>86633945</v>
+      </c>
+      <c r="B29" t="n">
+        <v>45297</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>208307</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Pudrad kärrtrollslända</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Leucorrhinia albifrons</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Burmeister, 1839)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skogsvägen Römossjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>634922</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6554572</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Göran E Holmberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Göran E Holmberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23846-2026 artfynd.xlsx
+++ b/artfynd/A 23846-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133920290</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80672131</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80672132</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80672309</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80672133</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80672192</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133920300</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1529,6 +1569,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133920310</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1643,6 +1688,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80828360</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1760,6 +1810,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85336564</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1869,6 +1924,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80672538</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1970,6 +2030,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80780664</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2079,6 +2144,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80780677</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2196,6 +2266,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85336525</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2305,6 +2380,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80672093</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2414,6 +2494,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80672518</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2523,6 +2608,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80672529</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2632,6 +2722,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80780864</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2739,6 +2834,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133920302</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2846,6 +2946,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133920308</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2958,6 +3063,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85356721</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3068,6 +3178,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80672511</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3178,6 +3293,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80780562</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3290,6 +3410,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133920298</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3402,6 +3527,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80779827</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3531,6 +3661,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317916</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3668,6 +3803,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86633955</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3805,8 +3945,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86633945</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>